--- a/braph2individualconnectome/pipelines/neuroimaging conversion PDFs/Example data NIfTI PDF shape covariation/reference_data/pdf_gmprob/sub-0001_ses-01_GMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion PDFs/Example data NIfTI PDF shape covariation/reference_data/pdf_gmprob/sub-0001_ses-01_GMprob_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -12980,7 +12979,7 @@
         <v>0</v>
       </c>
       <c r="AR36" s="0">
-        <v>0.037383177570093421</v>
+        <v>0.03738317757009342</v>
       </c>
       <c r="AS36" s="0">
         <v>0</v>
@@ -13827,7 +13826,7 @@
         <v>0</v>
       </c>
       <c r="CG38" s="0">
-        <v>1.1877326715121424</v>
+        <v>1.1877326715121423</v>
       </c>
       <c r="CH38" s="0">
         <v>0</v>
@@ -13973,7 +13972,7 @@
         <v>0</v>
       </c>
       <c r="M39" s="0">
-        <v>0.49896049896049855</v>
+        <v>0.49896049896049854</v>
       </c>
       <c r="N39" s="0">
         <v>0</v>
@@ -14042,7 +14041,7 @@
         <v>0</v>
       </c>
       <c r="AJ39" s="0">
-        <v>3.746130030959749</v>
+        <v>3.7461300309597489</v>
       </c>
       <c r="AK39" s="0">
         <v>8.4243369734789315</v>
@@ -14404,7 +14403,7 @@
         <v>0</v>
       </c>
       <c r="AJ40" s="0">
-        <v>8.7925696594427159</v>
+        <v>8.7925696594427158</v>
       </c>
       <c r="AK40" s="0">
         <v>12.903944729217727</v>
@@ -14623,7 +14622,7 @@
         <v>6.229508196721306</v>
       </c>
       <c r="DE40" s="0">
-        <v>8.8931851135814331</v>
+        <v>8.893185113581433</v>
       </c>
       <c r="DF40" s="0">
         <v>13.036809815950908</v>
@@ -14700,7 +14699,7 @@
         <v>6.7775467775468092</v>
       </c>
       <c r="N41" s="0">
-        <v>0.093457943925234086</v>
+        <v>0.093457943925234085</v>
       </c>
       <c r="O41" s="0">
         <v>0</v>
@@ -15526,7 +15525,7 @@
         <v>0.76038575667655717</v>
       </c>
       <c r="AV43" s="0">
-        <v>0.17885088307623504</v>
+        <v>0.17885088307623503</v>
       </c>
       <c r="AW43" s="0">
         <v>13.96663078579116</v>
@@ -15622,7 +15621,7 @@
         <v>12.631578947368411</v>
       </c>
       <c r="CB43" s="0">
-        <v>8.5039370078740078</v>
+        <v>8.5039370078740077</v>
       </c>
       <c r="CC43" s="0">
         <v>0</v>
@@ -15691,7 +15690,7 @@
         <v>0</v>
       </c>
       <c r="CY43" s="0">
-        <v>0.048626306831996064</v>
+        <v>0.048626306831996063</v>
       </c>
       <c r="CZ43" s="0">
         <v>6.9680727103239271</v>
@@ -15810,7 +15809,7 @@
         <v>3.9598438371444473</v>
       </c>
       <c r="V44" s="0">
-        <v>1.5165441176470576</v>
+        <v>1.5165441176470575</v>
       </c>
       <c r="W44" s="0">
         <v>0.051282051282051239</v>
@@ -16220,7 +16219,7 @@
         <v>0.2005794517494984</v>
       </c>
       <c r="AL45" s="0">
-        <v>8.3962081640549347</v>
+        <v>8.3962081640549346</v>
       </c>
       <c r="AM45" s="0">
         <v>1.4828544949026863</v>
@@ -16247,7 +16246,7 @@
         <v>15.692821368948234</v>
       </c>
       <c r="AU45" s="0">
-        <v>7.9191394658753636</v>
+        <v>7.9191394658753635</v>
       </c>
       <c r="AV45" s="0">
         <v>3.6440867426782884</v>
@@ -16274,7 +16273,7 @@
         <v>4.2788217369222918</v>
       </c>
       <c r="BD45" s="0">
-        <v>0.020554984583761545</v>
+        <v>0.020554984583761544</v>
       </c>
       <c r="BE45" s="0">
         <v>3.9849976558837286</v>
@@ -16457,7 +16456,7 @@
         <v>13.054830287206256</v>
       </c>
       <c r="DM45" s="0">
-        <v>18.589743589743574</v>
+        <v>18.589743589743573</v>
       </c>
       <c r="DN45" s="0">
         <v>17.578124999999986</v>
@@ -16654,7 +16653,7 @@
         <v>1.9903173749327578</v>
       </c>
       <c r="BJ46" s="0">
-        <v>2.3217247097844092</v>
+        <v>2.3217247097844091</v>
       </c>
       <c r="BK46" s="0">
         <v>0.74180919019163338</v>
@@ -16669,7 +16668,7 @@
         <v>4.998447687053706</v>
       </c>
       <c r="BO46" s="0">
-        <v>5.2009456264775365</v>
+        <v>5.2009456264775364</v>
       </c>
       <c r="BP46" s="0">
         <v>4.5194003527336815</v>
@@ -16684,7 +16683,7 @@
         <v>14.588634435962668</v>
       </c>
       <c r="BT46" s="0">
-        <v>4.2991605189519167</v>
+        <v>4.2991605189519166</v>
       </c>
       <c r="BU46" s="0">
         <v>0.093254585017096589</v>
@@ -16720,7 +16719,7 @@
         <v>0</v>
       </c>
       <c r="CF46" s="0">
-        <v>0.34542314335060415</v>
+        <v>0.34542314335060414</v>
       </c>
       <c r="CG46" s="0">
         <v>0.15954617975536237</v>
@@ -16732,7 +16731,7 @@
         <v>0.39933444259567352</v>
       </c>
       <c r="CJ46" s="0">
-        <v>0.031625553447185297</v>
+        <v>0.031625553447185296</v>
       </c>
       <c r="CK46" s="0">
         <v>0.37462750106428233</v>
@@ -16804,7 +16803,7 @@
         <v>0</v>
       </c>
       <c r="DH46" s="0">
-        <v>1.8716577540106934</v>
+        <v>1.8716577540106933</v>
       </c>
       <c r="DI46" s="0">
         <v>0</v>
@@ -16860,7 +16859,7 @@
         <v>3.820598006644536</v>
       </c>
       <c r="J47" s="0">
-        <v>16.324573182428623</v>
+        <v>16.324573182428622</v>
       </c>
       <c r="K47" s="0">
         <v>0</v>
@@ -16929,7 +16928,7 @@
         <v>17.263157894736921</v>
       </c>
       <c r="AG47" s="0">
-        <v>1.9918515165233231</v>
+        <v>1.991851516523323</v>
       </c>
       <c r="AH47" s="0">
         <v>13.415794481446303</v>
@@ -16953,7 +16952,7 @@
         <v>0.78226857887875212</v>
       </c>
       <c r="AO47" s="0">
-        <v>0.49438202247191238</v>
+        <v>0.49438202247191237</v>
       </c>
       <c r="AP47" s="0">
         <v>0.088300220750552286</v>
@@ -17013,7 +17012,7 @@
         <v>7.6807228915663011</v>
       </c>
       <c r="BI47" s="0">
-        <v>5.8418504572350996</v>
+        <v>5.8418504572350995</v>
       </c>
       <c r="BJ47" s="0">
         <v>0.57490326147042836</v>
@@ -17127,7 +17126,7 @@
         <v>4.225070084100941</v>
       </c>
       <c r="CU47" s="0">
-        <v>1.1976047904191674</v>
+        <v>1.1976047904191673</v>
       </c>
       <c r="CV47" s="0">
         <v>4.6641791044776344</v>
@@ -17207,7 +17206,7 @@
         <v>0</v>
       </c>
       <c r="E48" s="0">
-        <v>0.065414447247920699</v>
+        <v>0.065414447247920698</v>
       </c>
       <c r="F48" s="0">
         <v>0.034432297495050328</v>
@@ -17246,7 +17245,7 @@
         <v>0.92592592592592504</v>
       </c>
       <c r="R48" s="0">
-        <v>2.0661157024793369</v>
+        <v>2.0661157024793368</v>
       </c>
       <c r="S48" s="0">
         <v>17.107829478963485</v>
@@ -17255,7 +17254,7 @@
         <v>0.36877688998156083</v>
       </c>
       <c r="U48" s="0">
-        <v>7.9196876742888947</v>
+        <v>7.9196876742888946</v>
       </c>
       <c r="V48" s="0">
         <v>0</v>
@@ -17474,7 +17473,7 @@
         <v>0.013224014810896578</v>
       </c>
       <c r="CP48" s="0">
-        <v>9.3776232162129674</v>
+        <v>9.3776232162129673</v>
       </c>
       <c r="CQ48" s="0">
         <v>1.2841352405721707</v>
@@ -17486,10 +17485,10 @@
         <v>12.339672711189728</v>
       </c>
       <c r="CT48" s="0">
-        <v>1.3015618742490978</v>
+        <v>1.3015618742490977</v>
       </c>
       <c r="CU48" s="0">
-        <v>4.491017964071852</v>
+        <v>4.4910179640718519</v>
       </c>
       <c r="CV48" s="0">
         <v>10.261194029850738</v>
@@ -17782,7 +17781,7 @@
         <v>15.921052631578933</v>
       </c>
       <c r="BX49" s="0">
-        <v>8.2877576777450504</v>
+        <v>8.2877576777450503</v>
       </c>
       <c r="BY49" s="0">
         <v>3.09364548494983</v>
@@ -17848,7 +17847,7 @@
         <v>7.7178239716939334</v>
       </c>
       <c r="CT49" s="0">
-        <v>0.46055266319583455</v>
+        <v>0.46055266319583454</v>
       </c>
       <c r="CU49" s="0">
         <v>8.0838323353293333</v>
@@ -17908,7 +17907,7 @@
         <v>0.64102564102564041</v>
       </c>
       <c r="DN49" s="0">
-        <v>0.58593749999999945</v>
+        <v>0.58593749999999944</v>
       </c>
       <c r="DO49" s="0">
         <v>0.485436893203883</v>
@@ -18114,7 +18113,7 @@
         <v>0</v>
       </c>
       <c r="BN50" s="0">
-        <v>6.4265755976404782</v>
+        <v>6.4265755976404781</v>
       </c>
       <c r="BO50" s="0">
         <v>6.0114826072272827</v>
@@ -18168,7 +18167,7 @@
         <v>10.666666666666657</v>
       </c>
       <c r="CF50" s="0">
-        <v>17.789291882556118</v>
+        <v>17.789291882556117</v>
       </c>
       <c r="CG50" s="0">
         <v>0</v>
@@ -18201,7 +18200,7 @@
         <v>15.625374745173268</v>
       </c>
       <c r="CQ50" s="0">
-        <v>0.032509752925877739</v>
+        <v>0.032509752925877738</v>
       </c>
       <c r="CR50" s="0">
         <v>0.015979546180888447</v>
@@ -18419,7 +18418,7 @@
         <v>0</v>
       </c>
       <c r="AU51" s="0">
-        <v>0.24109792284866447</v>
+        <v>0.24109792284866446</v>
       </c>
       <c r="AV51" s="0">
         <v>0.76011625307399888</v>
@@ -18862,10 +18861,10 @@
         <v>13.894933167547393</v>
       </c>
       <c r="BV52" s="0">
-        <v>12.874692874692864</v>
+        <v>12.874692874692863</v>
       </c>
       <c r="BW52" s="0">
-        <v>4.5614035087719263</v>
+        <v>4.5614035087719262</v>
       </c>
       <c r="BX52" s="0">
         <v>11.737484223811517</v>
@@ -18949,7 +18948,7 @@
         <v>3.7871524448705625</v>
       </c>
       <c r="CY52" s="0">
-        <v>0.99683929005591943</v>
+        <v>0.99683929005591942</v>
       </c>
       <c r="CZ52" s="0">
         <v>0</v>
@@ -19293,7 +19292,7 @@
         <v>0</v>
       </c>
       <c r="CS53" s="0">
-        <v>0.044228217602830571</v>
+        <v>0.04422821760283057</v>
       </c>
       <c r="CT53" s="0">
         <v>0</v>
@@ -19607,13 +19606,13 @@
         <v>0</v>
       </c>
       <c r="CC54" s="0">
-        <v>0.07499062617172847</v>
+        <v>0.074990626171728469</v>
       </c>
       <c r="CD54" s="0">
         <v>0</v>
       </c>
       <c r="CE54" s="0">
-        <v>3.8095238095238067</v>
+        <v>3.8095238095238066</v>
       </c>
       <c r="CF54" s="0">
         <v>1.8998272884283232</v>
@@ -19951,7 +19950,7 @@
         <v>5.7493857493857439</v>
       </c>
       <c r="BW55" s="0">
-        <v>0.043859649122806981</v>
+        <v>0.04385964912280698</v>
       </c>
       <c r="BX55" s="0">
         <v>0.29448885149347892</v>
@@ -19978,7 +19977,7 @@
         <v>1.5238095238095224</v>
       </c>
       <c r="CF55" s="0">
-        <v>0.34542314335060415</v>
+        <v>0.34542314335060414</v>
       </c>
       <c r="CG55" s="0">
         <v>0</v>
@@ -20265,7 +20264,7 @@
         <v>0</v>
       </c>
       <c r="BG56" s="0">
-        <v>1.0720887245841027</v>
+        <v>1.0720887245841026</v>
       </c>
       <c r="BH56" s="0">
         <v>0</v>
@@ -20980,7 +20979,7 @@
         <v>0</v>
       </c>
       <c r="BD58" s="0">
-        <v>0.020554984583761545</v>
+        <v>0.020554984583761544</v>
       </c>
       <c r="BE58" s="0">
         <v>0</v>
@@ -23514,7 +23513,7 @@
         <v>0</v>
       </c>
       <c r="BD65" s="0">
-        <v>0.020554984583761545</v>
+        <v>0.020554984583761544</v>
       </c>
       <c r="BE65" s="0">
         <v>0</v>
@@ -24196,7 +24195,7 @@
         <v>0</v>
       </c>
       <c r="AP67" s="0">
-        <v>1.72185430463576</v>
+        <v>1.7218543046357599</v>
       </c>
       <c r="AQ67" s="0">
         <v>0</v>
@@ -24292,7 +24291,7 @@
         <v>0</v>
       </c>
       <c r="BV67" s="0">
-        <v>0.93366093366093284</v>
+        <v>0.93366093366093283</v>
       </c>
       <c r="BW67" s="0">
         <v>0</v>
@@ -24992,7 +24991,7 @@
         <v>0</v>
       </c>
       <c r="BN69" s="0">
-        <v>0.031046258925799757</v>
+        <v>0.031046258925799756</v>
       </c>
       <c r="BO69" s="0">
         <v>0</v>
@@ -25297,7 +25296,7 @@
         <v>0</v>
       </c>
       <c r="AU70" s="0">
-        <v>0.037091988130563768</v>
+        <v>0.037091988130563767</v>
       </c>
       <c r="AV70" s="0">
         <v>0.3353454057679407</v>
@@ -25659,7 +25658,7 @@
         <v>0</v>
       </c>
       <c r="AU71" s="0">
-        <v>0.24109792284866447</v>
+        <v>0.24109792284866446</v>
       </c>
       <c r="AV71" s="0">
         <v>1.6767270288397036</v>
@@ -25695,7 +25694,7 @@
         <v>0</v>
       </c>
       <c r="BG71" s="0">
-        <v>0.72088724584103448</v>
+        <v>0.72088724584103447</v>
       </c>
       <c r="BH71" s="0">
         <v>0</v>
@@ -26599,7 +26598,7 @@
         <v>0</v>
       </c>
       <c r="DO73" s="0">
-        <v>0.97087378640776601</v>
+        <v>0.970873786407766</v>
       </c>
       <c r="DP73" s="0">
         <v>0</v>
@@ -26763,7 +26762,7 @@
         <v>12.226750648388281</v>
       </c>
       <c r="BA74" s="0">
-        <v>3.082730418370554</v>
+        <v>3.0827304183705539</v>
       </c>
       <c r="BB74" s="0">
         <v>5.6179775280898827</v>
@@ -26772,7 +26771,7 @@
         <v>0.076180802437785619</v>
       </c>
       <c r="BD74" s="0">
-        <v>1.3155190133607389</v>
+        <v>1.3155190133607388</v>
       </c>
       <c r="BE74" s="0">
         <v>11.626816690107818</v>
@@ -26961,7 +26960,7 @@
         <v>0</v>
       </c>
       <c r="DO74" s="0">
-        <v>2.9126213592232984</v>
+        <v>2.9126213592232983</v>
       </c>
       <c r="DP74" s="0">
         <v>0</v>
@@ -27337,7 +27336,7 @@
         <v>1.7686904164576001</v>
       </c>
       <c r="C76" s="0">
-        <v>2.0768890852850182</v>
+        <v>2.0768890852850181</v>
       </c>
       <c r="D76" s="0">
         <v>0.59011556429800782</v>
@@ -27705,7 +27704,7 @@
         <v>1.9752479304974986</v>
       </c>
       <c r="E77" s="0">
-        <v>4.2986636762919313</v>
+        <v>4.2986636762919312</v>
       </c>
       <c r="F77" s="0">
         <v>1.8163036928639045</v>
@@ -28085,7 +28084,7 @@
         <v>0</v>
       </c>
       <c r="K78" s="0">
-        <v>5.0171037628278175</v>
+        <v>5.0171037628278174</v>
       </c>
       <c r="L78" s="0">
         <v>10.442194992008515</v>
@@ -28226,7 +28225,7 @@
         <v>0.60947022972339371</v>
       </c>
       <c r="BF78" s="0">
-        <v>0.29154518950437292</v>
+        <v>0.29154518950437291</v>
       </c>
       <c r="BG78" s="0">
         <v>0.406654343807763</v>
@@ -28295,7 +28294,7 @@
         <v>0</v>
       </c>
       <c r="CC78" s="0">
-        <v>8.0989876265466752</v>
+        <v>8.0989876265466751</v>
       </c>
       <c r="CD78" s="0">
         <v>0.53846153846153799</v>
@@ -28504,7 +28503,7 @@
         <v>0.78014184397163056</v>
       </c>
       <c r="AD79" s="0">
-        <v>0.071377587437544549</v>
+        <v>0.071377587437544548</v>
       </c>
       <c r="AE79" s="0">
         <v>0</v>
@@ -28615,7 +28614,7 @@
         <v>0.031046258925799413</v>
       </c>
       <c r="BO79" s="0">
-        <v>0.30395136778115473</v>
+        <v>0.30395136778115472</v>
       </c>
       <c r="BP79" s="0">
         <v>8.8403880070546652</v>
@@ -28672,7 +28671,7 @@
         <v>2.4109200496365872</v>
       </c>
       <c r="CH79" s="0">
-        <v>9.7522194249370529</v>
+        <v>9.7522194249370528</v>
       </c>
       <c r="CI79" s="0">
         <v>1.7637271214642247</v>
@@ -28833,7 +28832,7 @@
         <v>0</v>
       </c>
       <c r="S80" s="0">
-        <v>1.0587907495123981</v>
+        <v>1.058790749512398</v>
       </c>
       <c r="T80" s="0">
         <v>11.59598442942019</v>
@@ -28956,7 +28955,7 @@
         <v>0.018484288354898321</v>
       </c>
       <c r="BH80" s="0">
-        <v>8.902275769745641</v>
+        <v>8.9022757697456409</v>
       </c>
       <c r="BI80" s="0">
         <v>9.2630446476600241</v>
@@ -29025,7 +29024,7 @@
         <v>6.4615384615384555</v>
       </c>
       <c r="CE80" s="0">
-        <v>3.8095238095238067</v>
+        <v>3.8095238095238066</v>
       </c>
       <c r="CF80" s="0">
         <v>0.51813471502590625</v>
@@ -29040,7 +29039,7 @@
         <v>0.53244592346089803</v>
       </c>
       <c r="CJ80" s="0">
-        <v>0.031625553447185297</v>
+        <v>0.031625553447185296</v>
       </c>
       <c r="CK80" s="0">
         <v>0.31502767134951015</v>
@@ -29162,7 +29161,7 @@
         <v>9.1746794871794783</v>
       </c>
       <c r="H81" s="0">
-        <v>8.9009990917347786</v>
+        <v>8.9009990917347785</v>
       </c>
       <c r="I81" s="0">
         <v>10.249169435215936</v>
@@ -29270,7 +29269,7 @@
         <v>1.1587982832618016</v>
       </c>
       <c r="AR81" s="0">
-        <v>0.037383177570093421</v>
+        <v>0.03738317757009342</v>
       </c>
       <c r="AS81" s="0">
         <v>0</v>
@@ -29279,13 +29278,13 @@
         <v>0</v>
       </c>
       <c r="AU81" s="0">
-        <v>0.037091988130563768</v>
+        <v>0.037091988130563767</v>
       </c>
       <c r="AV81" s="0">
         <v>0</v>
       </c>
       <c r="AW81" s="0">
-        <v>5.1399354144241079</v>
+        <v>5.1399354144241078</v>
       </c>
       <c r="AX81" s="0">
         <v>8.7815253722272786</v>
@@ -29348,7 +29347,7 @@
         <v>0.50251256281406986</v>
       </c>
       <c r="BR81" s="0">
-        <v>2.0586098328893177</v>
+        <v>2.0586098328893176</v>
       </c>
       <c r="BS81" s="0">
         <v>0</v>
@@ -29390,7 +29389,7 @@
         <v>6.0952380952380896</v>
       </c>
       <c r="CF81" s="0">
-        <v>2.2452504317789273</v>
+        <v>2.2452504317789272</v>
       </c>
       <c r="CG81" s="0">
         <v>11.097323169650762</v>
@@ -29486,7 +29485,7 @@
         <v>0</v>
       </c>
       <c r="DL81" s="0">
-        <v>9.1383812010443784</v>
+        <v>9.1383812010443783</v>
       </c>
       <c r="DM81" s="0">
         <v>0</v>
@@ -29680,7 +29679,7 @@
         <v>0</v>
       </c>
       <c r="BH82" s="0">
-        <v>1.6900937081660144</v>
+        <v>1.6900937081660143</v>
       </c>
       <c r="BI82" s="0">
         <v>2.9478214093599009</v>
@@ -29782,7 +29781,7 @@
         <v>1.5604337476858134</v>
       </c>
       <c r="CP82" s="0">
-        <v>1.3670703921333634</v>
+        <v>1.3670703921333633</v>
       </c>
       <c r="CQ82" s="0">
         <v>0.16254876462939047</v>
@@ -29889,7 +29888,7 @@
         <v>7.5991522858007796</v>
       </c>
       <c r="I83" s="0">
-        <v>7.8405315614617877</v>
+        <v>7.8405315614617876</v>
       </c>
       <c r="J83" s="0">
         <v>6.0425858430845905</v>
@@ -29940,7 +29939,7 @@
         <v>8.9622641509433869</v>
       </c>
       <c r="Z83" s="0">
-        <v>5.0102951269732286</v>
+        <v>5.0102951269732285</v>
       </c>
       <c r="AA83" s="0">
         <v>0.2638522427440631</v>
@@ -30066,7 +30065,7 @@
         <v>0</v>
       </c>
       <c r="BP83" s="0">
-        <v>0.022045855379188691</v>
+        <v>0.02204585537918869</v>
       </c>
       <c r="BQ83" s="0">
         <v>0</v>
@@ -30111,13 +30110,13 @@
         <v>6.6923076923076863</v>
       </c>
       <c r="CE83" s="0">
-        <v>6.6666666666666608</v>
+        <v>6.6666666666666607</v>
       </c>
       <c r="CF83" s="0">
         <v>8.2901554404144999</v>
       </c>
       <c r="CG83" s="0">
-        <v>9.1650416592802611</v>
+        <v>9.165041659280261</v>
       </c>
       <c r="CH83" s="0">
         <v>0.13250298131707949</v>
@@ -30227,7 +30226,7 @@
     </row>
     <row r="84">
       <c r="A84" s="0">
-        <v>3.8642676005313335</v>
+        <v>3.8642676005313334</v>
       </c>
       <c r="B84" s="0">
         <v>0.075263421976919154</v>
@@ -30449,7 +30448,7 @@
         <v>0</v>
       </c>
       <c r="BW84" s="0">
-        <v>0.043859649122806981</v>
+        <v>0.04385964912280698</v>
       </c>
       <c r="BX84" s="0">
         <v>0</v>
@@ -30503,7 +30502,7 @@
         <v>0</v>
       </c>
       <c r="CO84" s="0">
-        <v>0.066120074054482878</v>
+        <v>0.066120074054482877</v>
       </c>
       <c r="CP84" s="0">
         <v>0.03597553663508811</v>
@@ -30613,13 +30612,13 @@
         <v>1.3321223130487423</v>
       </c>
       <c r="I85" s="0">
-        <v>0.96345514950166023</v>
+        <v>0.96345514950166022</v>
       </c>
       <c r="J85" s="0">
         <v>9.3995779781315854</v>
       </c>
       <c r="K85" s="0">
-        <v>0.17103762827822106</v>
+        <v>0.17103762827822105</v>
       </c>
       <c r="L85" s="0">
         <v>0.05327650506126793</v>
@@ -30811,7 +30810,7 @@
         <v>0</v>
       </c>
       <c r="BW85" s="0">
-        <v>0.043859649122806981</v>
+        <v>0.04385964912280698</v>
       </c>
       <c r="BX85" s="0">
         <v>0</v>
@@ -30951,7 +30950,7 @@
     </row>
     <row r="86">
       <c r="A86" s="0">
-        <v>0.18113754377490624</v>
+        <v>0.18113754377490623</v>
       </c>
       <c r="B86" s="0">
         <v>0</v>
@@ -30996,7 +30995,7 @@
         <v>2.6497923670160151</v>
       </c>
       <c r="P86" s="0">
-        <v>1.672069612694078</v>
+        <v>1.6720696126940779</v>
       </c>
       <c r="Q86" s="0">
         <v>0.61728395061728336</v>
@@ -31188,7 +31187,7 @@
         <v>0.75187969924811959</v>
       </c>
       <c r="CB86" s="0">
-        <v>6.1417322834645614</v>
+        <v>6.1417322834645613</v>
       </c>
       <c r="CC86" s="0">
         <v>0</v>
@@ -31203,7 +31202,7 @@
         <v>1.5544041450777188</v>
       </c>
       <c r="CG86" s="0">
-        <v>0.24818294628611926</v>
+        <v>0.24818294628611925</v>
       </c>
       <c r="CH86" s="0">
         <v>0</v>
@@ -31406,7 +31405,7 @@
         <v>1.2295081967213104</v>
       </c>
       <c r="AF87" s="0">
-        <v>2.105263157894735</v>
+        <v>2.1052631578947349</v>
       </c>
       <c r="AG87" s="0">
         <v>0</v>
@@ -31562,7 +31561,7 @@
         <v>0.1904761904761903</v>
       </c>
       <c r="CF87" s="0">
-        <v>0.34542314335060415</v>
+        <v>0.34542314335060414</v>
       </c>
       <c r="CG87" s="0">
         <v>0.070909413224605505</v>
@@ -31637,7 +31636,7 @@
         <v>2.2950819672131124</v>
       </c>
       <c r="DE87" s="0">
-        <v>0.1449975833736103</v>
+        <v>0.14499758337361029</v>
       </c>
       <c r="DF87" s="0">
         <v>0.20449897750511231</v>
@@ -32717,7 +32716,7 @@
         <v>0</v>
       </c>
       <c r="DC90" s="0">
-        <v>2.8513695554557677</v>
+        <v>2.8513695554557676</v>
       </c>
       <c r="DD90" s="0">
         <v>0</v>
@@ -33252,7 +33251,7 @@
         <v>0</v>
       </c>
       <c r="AR92" s="0">
-        <v>0.037383177570093421</v>
+        <v>0.03738317757009342</v>
       </c>
       <c r="AS92" s="0">
         <v>0</v>
@@ -33471,7 +33470,7 @@
         <v>0</v>
       </c>
       <c r="DM92" s="0">
-        <v>6.1965811965811915</v>
+        <v>6.1965811965811914</v>
       </c>
       <c r="DN92" s="0">
         <v>0</v>
